--- a/Observatorio_Trafico_Marbella_DGT.xlsx
+++ b/Observatorio_Trafico_Marbella_DGT.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Comparativa_2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Indicadores" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-10T11:14:38+00:00</t>
+          <t>2026-07-10T11:31:45+00:00</t>
         </is>
       </c>
     </row>

--- a/Observatorio_Trafico_Marbella_DGT.xlsx
+++ b/Observatorio_Trafico_Marbella_DGT.xlsx
@@ -1,18 +1,18 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Comparativa_2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Indicadores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="6" state="visible" r:id="rId6"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -555,7 +555,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-10T11:31:45+00:00</t>
+          <t>2026-07-10T11:39:44+00:00</t>
         </is>
       </c>
     </row>

--- a/Observatorio_Trafico_Marbella_DGT.xlsx
+++ b/Observatorio_Trafico_Marbella_DGT.xlsx
@@ -11,8 +11,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aforos_MA341_MA417" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -489,7 +490,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C14"/>
+  <dimension ref="B2:C15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -555,7 +556,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-10T11:39:44+00:00</t>
+          <t>2026-07-13T07:31:49+00:00</t>
         </is>
       </c>
     </row>
@@ -620,6 +621,18 @@
       <c r="C14" t="inlineStr">
         <is>
           <t>2015–2023 (9 años)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>Aforos de tráfico MA-341 / MA-417 (seguimiento propio)</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>2015–2024 (7 años)</t>
         </is>
       </c>
     </row>
@@ -4878,6 +4891,240 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:H10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+    <col width="11" customWidth="1" min="5" max="5"/>
+    <col width="11" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="11" customWidth="1" min="8" max="8"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Aforos MA341 MA417</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Ámbito: Marbella  ·  Fuente: DGT en cifras (Información municipal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2015</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2016</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2017</v>
+      </c>
+      <c r="E4" s="7" t="n">
+        <v>2018</v>
+      </c>
+      <c r="F4" s="7" t="n">
+        <v>2021</v>
+      </c>
+      <c r="G4" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="H4" s="7" t="n">
+        <v>2024</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>MA-341 · Ligeros</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>976464</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>1036714</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>1092052</v>
+      </c>
+      <c r="E5" s="9" t="n">
+        <v>1106548</v>
+      </c>
+      <c r="F5" s="9" t="n">
+        <v>1027831</v>
+      </c>
+      <c r="G5" s="9" t="n">
+        <v>1206710</v>
+      </c>
+      <c r="H5" s="9" t="n">
+        <v>1190250</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>MA-341 · Pesados</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>50351</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>62893</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>58545</v>
+      </c>
+      <c r="E6" s="9" t="n">
+        <v>60593</v>
+      </c>
+      <c r="F6" s="9" t="n">
+        <v>60319</v>
+      </c>
+      <c r="G6" s="9" t="n">
+        <v>71170</v>
+      </c>
+      <c r="H6" s="9" t="n">
+        <v>85102</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>MA-341 · Total</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>1031065</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>1099606</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>1150604</v>
+      </c>
+      <c r="E7" s="9" t="n">
+        <v>1167148</v>
+      </c>
+      <c r="F7" s="9" t="n">
+        <v>1088156</v>
+      </c>
+      <c r="G7" s="9" t="n">
+        <v>1277882</v>
+      </c>
+      <c r="H7" s="9" t="n">
+        <v>1275349</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>MA-417 · Ligeros</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>784465</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>825742</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>820513</v>
+      </c>
+      <c r="E8" s="9" t="n">
+        <v>813406</v>
+      </c>
+      <c r="F8" s="9" t="n">
+        <v>737711</v>
+      </c>
+      <c r="G8" s="9" t="n">
+        <v>872414</v>
+      </c>
+      <c r="H8" s="9" t="n">
+        <v>884462</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>MA-417 · Pesados</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>41831</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>38237</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>41941</v>
+      </c>
+      <c r="E9" s="9" t="n">
+        <v>42974</v>
+      </c>
+      <c r="F9" s="9" t="n">
+        <v>41092</v>
+      </c>
+      <c r="G9" s="9" t="n">
+        <v>69453</v>
+      </c>
+      <c r="H9" s="9" t="n">
+        <v>76962</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>MA-417 · Total</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>829751</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>863979</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>862460</v>
+      </c>
+      <c r="E10" s="9" t="n">
+        <v>856387</v>
+      </c>
+      <c r="F10" s="9" t="n">
+        <v>778812</v>
+      </c>
+      <c r="G10" s="9" t="n">
+        <v>941866</v>
+      </c>
+      <c r="H10" s="9" t="n">
+        <v>961426</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5174,7 +5421,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Observatorio_Trafico_Marbella_DGT.xlsx
+++ b/Observatorio_Trafico_Marbella_DGT.xlsx
@@ -12,8 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aforos_MA341_MA417" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criminalidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -490,7 +491,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="B2:C15"/>
+  <dimension ref="B2:C16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="3" customWidth="1" min="1" max="1"/>
@@ -556,7 +557,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-13T07:31:49+00:00</t>
+          <t>2026-07-13T09:21:24+00:00</t>
         </is>
       </c>
     </row>
@@ -633,6 +634,18 @@
       <c r="C15" t="inlineStr">
         <is>
           <t>2015–2024 (7 años)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>Criminalidad (Ministerio del Interior)</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>2023–2025 (3 años)</t>
         </is>
       </c>
     </row>
@@ -5125,6 +5138,360 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:D23"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="42" customWidth="1" min="1" max="1"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="5" t="inlineStr">
+        <is>
+          <t>Criminalidad</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="6" t="inlineStr">
+        <is>
+          <t>Ámbito: Marbella  ·  Fuente: DGT en cifras (Información municipal)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="7" t="inlineStr">
+        <is>
+          <t>Indicador</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="n">
+        <v>2023</v>
+      </c>
+      <c r="C4" s="7" t="n">
+        <v>2024</v>
+      </c>
+      <c r="D4" s="7" t="n">
+        <v>2025</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>Criminalidad convencional (total)</t>
+        </is>
+      </c>
+      <c r="B5" s="9" t="n">
+        <v>11844</v>
+      </c>
+      <c r="C5" s="9" t="n">
+        <v>11988</v>
+      </c>
+      <c r="D5" s="9" t="n">
+        <v>12098</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Homicidios dolosos y asesinatos consumados</t>
+        </is>
+      </c>
+      <c r="B6" s="9" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" s="9" t="n">
+        <v>2</v>
+      </c>
+      <c r="D6" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Homicidios dolosos y asesinatos en grado tentativa</t>
+        </is>
+      </c>
+      <c r="B7" s="9" t="n">
+        <v>5</v>
+      </c>
+      <c r="C7" s="9" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="9" t="n">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>Delitos graves y menos graves de lesiones y riña tumultuaria</t>
+        </is>
+      </c>
+      <c r="B8" s="9" t="n">
+        <v>123</v>
+      </c>
+      <c r="C8" s="9" t="n">
+        <v>139</v>
+      </c>
+      <c r="D8" s="9" t="n">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>Secuestro</t>
+        </is>
+      </c>
+      <c r="B9" s="9" t="n">
+        <v>1</v>
+      </c>
+      <c r="C9" s="9" t="n">
+        <v>4</v>
+      </c>
+      <c r="D9" s="9" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>Delitos contra la libertad sexual</t>
+        </is>
+      </c>
+      <c r="B10" s="9" t="n">
+        <v>95</v>
+      </c>
+      <c r="C10" s="9" t="n">
+        <v>93</v>
+      </c>
+      <c r="D10" s="9" t="n">
+        <v>113</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>Agresión sexual con penetración</t>
+        </is>
+      </c>
+      <c r="B11" s="9" t="n">
+        <v>32</v>
+      </c>
+      <c r="C11" s="9" t="n">
+        <v>22</v>
+      </c>
+      <c r="D11" s="9" t="n">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Resto de delitos contra la libertad sexual</t>
+        </is>
+      </c>
+      <c r="B12" s="9" t="n">
+        <v>63</v>
+      </c>
+      <c r="C12" s="9" t="n">
+        <v>71</v>
+      </c>
+      <c r="D12" s="9" t="n">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>Robos con violencia e intimidación</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
+        <v>284</v>
+      </c>
+      <c r="C13" s="9" t="n">
+        <v>257</v>
+      </c>
+      <c r="D13" s="9" t="n">
+        <v>275</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>Robos con fuerza en domicilios, establecimientos y otras instalaciones</t>
+        </is>
+      </c>
+      <c r="B14" s="9" t="n">
+        <v>817</v>
+      </c>
+      <c r="C14" s="9" t="n">
+        <v>686</v>
+      </c>
+      <c r="D14" s="9" t="n">
+        <v>505</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>Robos con fuerza en domicilios</t>
+        </is>
+      </c>
+      <c r="B15" s="9" t="n">
+        <v>629</v>
+      </c>
+      <c r="C15" s="9" t="n">
+        <v>523</v>
+      </c>
+      <c r="D15" s="9" t="n">
+        <v>413</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>Hurtos</t>
+        </is>
+      </c>
+      <c r="B16" s="9" t="n">
+        <v>3623</v>
+      </c>
+      <c r="C16" s="9" t="n">
+        <v>3749</v>
+      </c>
+      <c r="D16" s="9" t="n">
+        <v>3747</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>Sustracciones de vehículos</t>
+        </is>
+      </c>
+      <c r="B17" s="9" t="n">
+        <v>355</v>
+      </c>
+      <c r="C17" s="9" t="n">
+        <v>364</v>
+      </c>
+      <c r="D17" s="9" t="n">
+        <v>326</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>Tráfico de drogas</t>
+        </is>
+      </c>
+      <c r="B18" s="9" t="n">
+        <v>146</v>
+      </c>
+      <c r="C18" s="9" t="n">
+        <v>150</v>
+      </c>
+      <c r="D18" s="9" t="n">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>Resto de criminalidad CONVENCIONAL</t>
+        </is>
+      </c>
+      <c r="B19" s="9" t="n">
+        <v>6392</v>
+      </c>
+      <c r="C19" s="9" t="n">
+        <v>6544</v>
+      </c>
+      <c r="D19" s="9" t="n">
+        <v>6807</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>Cibercriminalidad (total)</t>
+        </is>
+      </c>
+      <c r="B20" s="9" t="n">
+        <v>1794</v>
+      </c>
+      <c r="C20" s="9" t="n">
+        <v>1753</v>
+      </c>
+      <c r="D20" s="9" t="n">
+        <v>2051</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Estafas informáticas</t>
+        </is>
+      </c>
+      <c r="B21" s="9" t="n">
+        <v>1588</v>
+      </c>
+      <c r="C21" s="9" t="n">
+        <v>1483</v>
+      </c>
+      <c r="D21" s="9" t="n">
+        <v>1713</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>Otros ciberdelitos</t>
+        </is>
+      </c>
+      <c r="B22" s="9" t="n">
+        <v>206</v>
+      </c>
+      <c r="C22" s="9" t="n">
+        <v>270</v>
+      </c>
+      <c r="D22" s="9" t="n">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>TOTAL criminalidad</t>
+        </is>
+      </c>
+      <c r="B23" s="9" t="n">
+        <v>13638</v>
+      </c>
+      <c r="C23" s="9" t="n">
+        <v>13741</v>
+      </c>
+      <c r="D23" s="9" t="n">
+        <v>14149</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -5421,7 +5788,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>

--- a/Observatorio_Trafico_Marbella_DGT.xlsx
+++ b/Observatorio_Trafico_Marbella_DGT.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Portada" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Aforos_MA341_MA417" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Criminalidad" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Comparativa_2025" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Indicadores" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Portada" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="General_Marbella" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Siniestralidad_Marbella" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Sanciones_Marbella" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Aforos_MA341_MA417" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="Criminalidad" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="Comparativa_2025" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="Indicadores" sheetId="8" state="visible" r:id="rId8"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -557,7 +557,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>2026-07-13T09:21:24+00:00</t>
+          <t>2026-07-13T09:29:58+00:00</t>
         </is>
       </c>
     </row>
